--- a/burger_king_light/WBBOMDesign28.xlsx
+++ b/burger_king_light/WBBOMDesign28.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\one-off-pcbs\burger_king_light\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B21A4570-550A-4976-ACB4-29E5DA958676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{861A866B-8D93-4244-8211-31C17D375A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500"/>
   </bookViews>
   <sheets>
     <sheet name="WBBOMDesign28" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">WBBOMDesign28!$A$1:$G$1</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -118,15 +121,6 @@
     <t>D1</t>
   </si>
   <si>
-    <t>Diodes Inc.</t>
-  </si>
-  <si>
-    <t>B540C-13-F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type: Schottky  VRRM: 40 V  Io: 5 A  </t>
-  </si>
-  <si>
     <t>Rt</t>
   </si>
   <si>
@@ -194,6 +188,15 @@
   </si>
   <si>
     <t xml:space="preserve">Cap: 2.2 µF  Total Derated Cap: 600 nF  VDC: 50 V  ESR: 3.47 mΩ  Package: 0805  </t>
+  </si>
+  <si>
+    <t>CDBA540-HF</t>
+  </si>
+  <si>
+    <t>Comchip Technology</t>
+  </si>
+  <si>
+    <t>DIODE SCHOTTKY 40V 5A DO214AC</t>
   </si>
 </sst>
 </file>
@@ -1038,8 +1041,8 @@
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.08984375" customWidth="1"/>
+    <col min="2" max="2" width="21.36328125" customWidth="1"/>
     <col min="3" max="3" width="21.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.81640625" bestFit="1" customWidth="1"/>
@@ -1072,197 +1075,194 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="F2">
         <v>10.92</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="F3">
-        <v>10.92</v>
+        <v>6.75</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
-        <v>0.1</v>
+        <v>0.34</v>
       </c>
       <c r="F4">
-        <v>10.92</v>
+        <v>23.1</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>0.34</v>
+        <v>0.01</v>
       </c>
       <c r="F5">
-        <v>23.1</v>
+        <v>6.75</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>0.01</v>
+        <v>0.45669999999999999</v>
       </c>
       <c r="F6">
-        <v>10.92</v>
+        <v>58.4</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
-        <v>0.18</v>
-      </c>
-      <c r="F7" t="s">
-        <v>29</v>
+        <v>0.13269</v>
+      </c>
+      <c r="F7">
+        <v>6.75</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>0.19</v>
-      </c>
-      <c r="F8">
-        <v>83.27</v>
+        <v>0.18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>0.01</v>
-      </c>
-      <c r="F9">
-        <v>10.92</v>
+        <v>0.77</v>
       </c>
       <c r="G9" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1274,41 +1274,41 @@
         <v>75.040000000000006</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F11">
-        <v>6.75</v>
+        <v>10.92</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1317,79 +1317,84 @@
         <v>0.01</v>
       </c>
       <c r="F12">
-        <v>6.75</v>
+        <v>10.92</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13">
-        <v>0.45669999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="F13">
-        <v>58.4</v>
+        <v>10.92</v>
       </c>
       <c r="G13" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14">
-        <v>1.169</v>
+        <v>0.01</v>
       </c>
       <c r="F14">
-        <v>16</v>
+        <v>10.92</v>
+      </c>
+      <c r="G14" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>0.13269</v>
+        <v>1.169</v>
       </c>
       <c r="F15">
-        <v>6.75</v>
-      </c>
-      <c r="G15" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G15">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>